--- a/data/trans_orig/IP07C03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C03-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18988</t>
+          <t>18999</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29309</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16409</t>
+          <t>16846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27357</t>
+          <t>26999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38728</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53577</t>
+          <t>54341</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23264</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>25298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30174</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45167</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88696</t>
+          <t>88861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111198</t>
+          <t>110123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99617</t>
+          <t>98743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122048</t>
+          <t>122601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>195908</t>
+          <t>195838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>226376</t>
+          <t>225929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67990</t>
+          <t>68331</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90531</t>
+          <t>89791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81509</t>
+          <t>80948</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104449</t>
+          <t>104838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156027</t>
+          <t>158010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187105</t>
+          <t>187707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,1%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27800</t>
+          <t>27358</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31693</t>
+          <t>31550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19768</t>
+          <t>19835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43646</t>
+          <t>43365</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60504</t>
+          <t>59910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>17543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29722</t>
+          <t>29212</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36439</t>
+          <t>36591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53135</t>
+          <t>53145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10735</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136044</t>
+          <t>134971</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163485</t>
+          <t>162810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144211</t>
+          <t>144813</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>172413</t>
+          <t>172218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>288252</t>
+          <t>289017</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>326861</t>
+          <t>327604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107415</t>
+          <t>107607</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>132846</t>
+          <t>134436</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>119161</t>
+          <t>120443</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148132</t>
+          <t>148098</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235800</t>
+          <t>235121</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>273946</t>
+          <t>274062</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22027</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38783</t>
+          <t>38337</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>12018</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>23258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>26039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41087</t>
+          <t>41663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26902</t>
+          <t>26626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38140</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17975</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29371</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48587</t>
+          <t>47967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64326</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58985</t>
+          <t>58529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80658</t>
+          <t>80802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96085</t>
+          <t>97093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121001</t>
+          <t>120999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161931</t>
+          <t>161116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195723</t>
+          <t>194647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108414</t>
+          <t>107850</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130876</t>
+          <t>130482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91652</t>
+          <t>92603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117169</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>206445</t>
+          <t>207789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240133</t>
+          <t>241268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,84%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15021</t>
+          <t>14514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25753</t>
+          <t>26300</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32780</t>
+          <t>32142</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18283</t>
+          <t>18262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42175</t>
+          <t>41226</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59664</t>
+          <t>59637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22311</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35264</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34248</t>
+          <t>34580</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47868</t>
+          <t>48327</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65896</t>
+          <t>66104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98087</t>
+          <t>97841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124966</t>
+          <t>124482</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135170</t>
+          <t>135433</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>165059</t>
+          <t>163032</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>240732</t>
+          <t>242737</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>284972</t>
+          <t>283460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>165690</t>
+          <t>166414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194474</t>
+          <t>194426</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>141861</t>
+          <t>143213</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170151</t>
+          <t>171316</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>314991</t>
+          <t>316568</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>358204</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22352</t>
+          <t>22909</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>21048</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>18706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24131</t>
+          <t>24272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>26306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39468</t>
+          <t>39586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18365</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10735</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22518</t>
+          <t>22671</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35884</t>
+          <t>35778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114343</t>
+          <t>112955</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139380</t>
+          <t>138831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115444</t>
+          <t>113790</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140044</t>
+          <t>140435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236874</t>
+          <t>235335</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>272914</t>
+          <t>272316</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,61%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88315</t>
+          <t>89528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113033</t>
+          <t>115451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79853</t>
+          <t>79408</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104286</t>
+          <t>104651</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>175242</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>211410</t>
+          <t>211981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18494</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20813</t>
+          <t>21240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36172</t>
+          <t>35958</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28532</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42731</t>
+          <t>42095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40977</t>
+          <t>39674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55276</t>
+          <t>54110</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73401</t>
+          <t>73233</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92536</t>
+          <t>93311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>24003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37441</t>
+          <t>37500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>32859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45800</t>
+          <t>45969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65237</t>
+          <t>65569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>160790</t>
+          <t>160778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190672</t>
+          <t>191182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>178840</t>
+          <t>179384</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>208334</t>
+          <t>209728</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>350503</t>
+          <t>348197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>393340</t>
+          <t>392057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>128979</t>
+          <t>130300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>159386</t>
+          <t>161745</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>119224</t>
+          <t>118549</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>149101</t>
+          <t>147671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>257244</t>
+          <t>256623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>299951</t>
+          <t>299379</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28004</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49594</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,47 +9085,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>6162</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>6162</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>2910</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>11248</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C03-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la menor [KIDSCREEN 20] en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21947</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16690</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27224</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24324</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18999</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29939</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18884</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29387</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,86%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21947</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>16846</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>26999</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,78%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38822</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54341</t>
+          <t>53257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>59,68%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19930</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14974</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25706</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17801</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12745</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23160</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13049</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23170</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19930</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14801</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25298</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>46,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>30946</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>45452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3368</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3206</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7019</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6580</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,97%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3691</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -1066,102 +1066,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3367</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4885</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4418</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4764</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>110401</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>97472</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>121499</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>99973</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88861</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>110123</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>89622</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>110948</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>110401</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>98743</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>122601</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,92%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>195838</t>
+          <t>194926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225929</t>
+          <t>226704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,67%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>92998</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>81805</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>105278</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>48,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>79044</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>68331</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89791</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>68627</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>89703</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>41,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>92998</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>80948</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>104838</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>42,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158010</t>
+          <t>155416</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187707</t>
+          <t>187277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10072</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6237</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16282</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9763</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5682</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15711</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5703</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15104</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,13%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10072</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5694</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15941</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27358</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3361</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1606</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5698</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3361</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1249</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6893</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>9452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>216831</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>216831</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>216831</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>190386</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>216831</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>216831</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>216831</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25925</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20341</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31828</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,86%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>25678</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19956</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31550</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19447</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>32020</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>47,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>25925</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19835</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31110</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,86%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43365</t>
+          <t>44003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59910</t>
+          <t>59745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20985</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15409</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26630</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,79%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54,3%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>23524</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17543</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29212</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17556</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>29680</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>43,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>20985</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>15514</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>26572</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>42,79%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36591</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53145</t>
+          <t>52814</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,13%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2131</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5709</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3665</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1322</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8331</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5709</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3756</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3012</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3299</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -2538,107 +2538,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3309</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3625</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,34%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3599</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>158272</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>145021</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>172315</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>51,21%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>46,92%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>55,75%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>149975</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>134971</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>162810</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>136656</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>164260</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>51,6%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>46,44%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>56,02%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>158272</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>144813</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>172218</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>51,21%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>289017</t>
+          <t>289601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>327604</t>
+          <t>326868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>133913</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>120072</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>147270</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>43,32%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>38,85%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>47,65%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>120368</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>107607</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>134436</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>106043</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>133699</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>41,41%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>46,25%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>133913</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>120443</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>148098</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>43,32%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235121</t>
+          <t>235468</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274062</t>
+          <t>271873</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>12870</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>7976</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>18482</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>16633</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>11171</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>24387</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>10770</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>23190</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>5,72%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>12870</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>8295</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>19106</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>38326</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4040</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8105</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2943</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6968</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7385</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1439</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8808</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3220,92 +3220,92 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3129</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3647</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>309095</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>309095</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>309095</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>432</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>290646</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>309095</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>309095</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>309095</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la menor [KIDSCREEN 20] en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17127</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12177</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22847</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,92%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>16529</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11574</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22418</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11255</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22750</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>32,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17127</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12018</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>23258</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,92%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26039</t>
+          <t>25782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41663</t>
+          <t>41995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23671</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17930</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28746</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>63,65%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32884</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26626</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38363</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>26255</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>38187</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,7%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>51,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23671</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17812</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>29405</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>52,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47967</t>
+          <t>48287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64716</t>
+          <t>64808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,96%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2683</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,27%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1477</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5037</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4993</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,86%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2683</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6404</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -4025,102 +4025,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>736</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3729</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4025</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1594</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6041</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1594</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5279</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -4133,107 +4133,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>823</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4313</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51626</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108518</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95472</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>120386</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>48,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>42,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>69422</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>58529</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80802</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>59250</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>80851</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,88%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>108518</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>97093</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>120999</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>48,13%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161116</t>
+          <t>161793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194647</t>
+          <t>193785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>104507</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>92855</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>117547</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>52,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>119235</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>107850</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>130482</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>108203</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>131279</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>59,9%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>54,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>65,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>104507</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>92603</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>116883</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>46,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207789</t>
+          <t>207209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>241268</t>
+          <t>239831</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9330</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5244</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14712</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8963</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5301</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14377</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5295</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15346</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,5%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9330</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5209</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14514</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>11967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>26100</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3098</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6940</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1427</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5260</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5407</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3098</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1155</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6921</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>225452</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>225452</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>225452</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>199047</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>199047</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>199047</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>225452</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>225452</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>225452</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5050,67 +5050,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>24452</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18542</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30460</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,02%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>54,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>25673</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19203</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>32142</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18938</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>32140</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>42,7%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24452</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18262</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30603</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>43,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41226</t>
+          <t>41402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>58992</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28107</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22266</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34752</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>50,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>39,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>61,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>28821</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22429</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>35809</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22849</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>36809</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>47,93%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>59,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>28107</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>22217</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>34580</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>50,06%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48327</t>
+          <t>48296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66104</t>
+          <t>65825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,61%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7488</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3642</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7870</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,09%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3029</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7123</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -5384,107 +5384,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1397</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4725</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5666</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,32%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2503</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5181</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>4,46%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5556</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -5497,107 +5497,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>594</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3460</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>2424</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>60126</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>60126</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>60126</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>150097</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>135334</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>164015</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>45,93%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>41,42%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>50,19%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>111624</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>97841</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>124482</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>98556</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>125722</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>35,92%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>31,48%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>40,05%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>150097</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>135433</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>163032</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>45,93%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>242737</t>
+          <t>242066</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>283460</t>
+          <t>284343</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,6%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>156285</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>141797</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>170867</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>43,39%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>52,29%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>180939</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>166414</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>194426</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>164975</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>193793</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>58,22%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>53,54%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>62,56%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>156285</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>143213</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>171316</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>47,83%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>316568</t>
+          <t>314446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>356943</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>15042</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>10191</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>22855</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>14081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>9055</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>20886</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>8694</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>21809</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>4,53%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>15042</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>9687</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>22909</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21048</t>
+          <t>21017</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38520</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4519</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>3560</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7828</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7870</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>4519</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8848</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>14028</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -6184,102 +6184,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4144</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3566</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4077</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5415</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1417</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4790</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>326766</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>326766</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>326766</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>310798</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>310798</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>310798</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>326766</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>326766</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>326766</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la menor [KIDSCREEN 20] en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19097</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13809</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24265</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13435</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8915</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18706</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9027</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17987</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>43,9%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19097</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14105</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24272</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,12%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26306</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>39569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15690</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10549</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20854</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13612</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8465</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18098</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9389</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18296</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15690</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10735</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20442</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>42,83%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22671</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35778</t>
+          <t>35787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4937</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2942</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7310</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7051</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>9,61%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5624</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -6979,107 +6979,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3169</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4349</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3478</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>127474</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>113902</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>139520</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>126584</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>112955</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>138831</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>113227</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>139778</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,88%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>127474</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>113790</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>140435</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>53,77%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>235335</t>
+          <t>235617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>272316</t>
+          <t>273063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>92462</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>80881</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>106049</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,12%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>100815</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>89528</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>115451</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>88140</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>113620</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>41,32%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>92462</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>79408</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>104651</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174909</t>
+          <t>175391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>211981</t>
+          <t>212049</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14179</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9006</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21026</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>12096</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7207</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18770</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18279</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14179</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9377</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21240</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35958</t>
+          <t>35227</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5785</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3488</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1161</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7788</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1177</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8176</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -7779,102 +7779,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3593</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5557</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4884</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4453</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>7022</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>237063</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>237063</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>237063</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>243998</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>243998</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>243998</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>237063</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>237063</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>237063</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47882</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41016</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>53959</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,32%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>71,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>35409</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28186</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42095</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28653</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42511</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>49,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>59,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>47882</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>39674</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>54110</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73233</t>
+          <t>72931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93311</t>
+          <t>93478</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,77%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24945</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18709</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31746</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,04%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>30583</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24003</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>37500</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>23740</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>37396</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>43,02%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>52,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>24945</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>18625</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>32859</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>33,04%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45969</t>
+          <t>45873</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65569</t>
+          <t>65741</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5646</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4460</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8551</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8447</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,27%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -8461,102 +8461,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>638</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3534</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2972</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4416</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4258</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>194453</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>178748</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>210612</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>55,68%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>51,19%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>60,31%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>175427</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>160778</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>191182</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>158063</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>189184</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>50,75%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>46,51%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>55,3%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>194453</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>179384</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>209728</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>55,68%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>348197</t>
+          <t>346752</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>392057</t>
+          <t>391369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>133098</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>118302</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>149094</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>38,11%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>33,88%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>42,7%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>145010</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>130300</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>161745</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>130633</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>160909</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>41,95%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>37,69%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>46,79%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>133098</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>118549</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>147671</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>38,11%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>256623</t>
+          <t>257622</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>299379</t>
+          <t>301458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>18129</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>12063</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>25535</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>19498</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>13006</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>26796</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>13307</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>26509</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>5,64%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>18129</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>12013</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>25884</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28997</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48397</t>
+          <t>48548</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5622</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>4105</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1739</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>9029</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1566</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>9084</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5522</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -9143,67 +9143,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5587</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>1653</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>6023</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5983</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5721</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>345694</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>345694</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>345694</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
